--- a/data/trans_bre/P19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,61</t>
+          <t>-1,8; 2,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,8</t>
+          <t>-1,97; 2,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,75</t>
+          <t>-0,01; 4,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,48</t>
+          <t>-4,4; 1,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 112,13</t>
+          <t>-42,84; 126,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 68,73</t>
+          <t>-45,11; 78,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 280,06</t>
+          <t>-2,03; 258,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 55,52</t>
+          <t>-64,73; 57,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,67</t>
+          <t>-3,06; 0,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,75</t>
+          <t>-0,12; 3,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,45</t>
+          <t>-2,1; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,35</t>
+          <t>-0,22; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 28,91</t>
+          <t>-61,33; 34,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 176,77</t>
+          <t>-6,71; 188,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 55,32</t>
+          <t>-46,57; 57,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 309,6</t>
+          <t>-10,71; 291,47</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,3</t>
+          <t>-1,92; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,47</t>
+          <t>-3,73; 0,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,84</t>
+          <t>-0,28; 4,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,63</t>
+          <t>-4,92; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 103,83</t>
+          <t>-45,96; 103,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 25,36</t>
+          <t>-72,98; 19,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 284,65</t>
+          <t>-15,82; 301,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 36,81</t>
+          <t>-64,25; 37,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,59</t>
+          <t>-1,04; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,96</t>
+          <t>-1,67; 2,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,92</t>
+          <t>-1,36; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,16</t>
+          <t>-0,08; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 117,23</t>
+          <t>-27,05; 111,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 79,25</t>
+          <t>-36,03; 86,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 120,82</t>
+          <t>-43,51; 107,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 189,79</t>
+          <t>-7,07; 210,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,0</t>
+          <t>-0,96; 1,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,21</t>
+          <t>-0,7; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,65</t>
+          <t>-0,13; 1,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,86</t>
+          <t>-0,65; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 33,87</t>
+          <t>-24,1; 36,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 43,33</t>
+          <t>-19,19; 41,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 67,6</t>
+          <t>-3,05; 71,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 70,99</t>
+          <t>-15,71; 67,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,49%</t>
+          <t>-14,34%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,75</t>
+          <t>-1,91; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,04</t>
+          <t>-1,99; 2,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,54</t>
+          <t>-0,04; 4,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,55</t>
+          <t>-3,42; 1,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 126,47</t>
+          <t>-43,93; 107,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 78,45</t>
+          <t>-45,3; 82,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 258,58</t>
+          <t>-6,28; 262,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 57,38</t>
+          <t>-55,85; 57,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,9</t>
+          <t>-3,06; 0,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,75</t>
+          <t>-0,16; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,4</t>
+          <t>-2,14; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,49</t>
+          <t>-0,33; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 34,66</t>
+          <t>-60,58; 26,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 188,71</t>
+          <t>-8,06; 165,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 57,79</t>
+          <t>-46,28; 51,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 291,47</t>
+          <t>-15,65; 149,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,58%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,34</t>
+          <t>-1,87; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,32</t>
+          <t>-3,74; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,04</t>
+          <t>-0,36; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 1,68</t>
+          <t>-2,54; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 103,42</t>
+          <t>-45,11; 106,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,98; 19,99</t>
+          <t>-71,28; 22,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 301,09</t>
+          <t>-17,41; 278,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,25; 37,74</t>
+          <t>-35,61; 55,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,66</t>
+          <t>-0,95; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,13</t>
+          <t>-1,52; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,89</t>
+          <t>-1,33; 1,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,31</t>
+          <t>0,08; 3,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 111,58</t>
+          <t>-26,96; 123,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 86,81</t>
+          <t>-35,72; 75,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,51; 107,42</t>
+          <t>-42,49; 90,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 210,87</t>
+          <t>-1,78; 198,69</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,07</t>
+          <t>-0,98; 1,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,21</t>
+          <t>-0,74; 1,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,66</t>
+          <t>-0,29; 1,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,79</t>
+          <t>-0,34; 1,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 36,01</t>
+          <t>-24,35; 39,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 41,98</t>
+          <t>-19,52; 41,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 71,44</t>
+          <t>-8,54; 68,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 67,38</t>
+          <t>-8,2; 59,2</t>
         </is>
       </c>
     </row>
